--- a/artfynd/A 46741-2024 artfynd.xlsx
+++ b/artfynd/A 46741-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2017,122 +2017,6 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>114700435</v>
-      </c>
-      <c r="B12" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Vattholma gård, 1,6 km NO-ut, Upl</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>655903</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6657665</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Rasbokil</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>C-Upp-0984</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2016-08-28</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2016-08-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Skogen här har avverkningsanmälts 2016-07-21 av Sveaskog. Knärotsbeståndet sitter i ett litet hänsynssnitslat område rikt på stenblock.</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Ingvar Sundh</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Jörgen Sjöström, Thorleif Joelson, Mattias Lif</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
